--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_i_peringr_median_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_i_peringr_median_a_2021_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:44</t>
+    <t xml:space="preserve">2026-09-18 09:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_i_peringr_median_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_i_peringr_median_a_2021_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:04</t>
+    <t xml:space="preserve">2026-10-05 04:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
